--- a/update.xlsx
+++ b/update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dchholdingsltd-my.sharepoint.com/personal/kimtsang_dchauriga_com/Documents/Documents/AI Transportation KPI Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{C7812C41-A0D8-4678-A7FF-CC765441959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB8B75FC-E18B-461A-88B7-9BFC92427D31}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{C7812C41-A0D8-4678-A7FF-CC765441959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956D3AEE-A247-497E-86A9-6C88E7818173}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2025,32 +2025,80 @@
       <c r="A15" s="9">
         <v>46235</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
+      <c r="B15" s="6">
+        <v>10227</v>
+      </c>
+      <c r="C15" s="6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="E15" s="6">
+        <v>8.1</v>
+      </c>
+      <c r="F15" s="6">
+        <v>43634</v>
+      </c>
+      <c r="G15" s="6">
+        <v>3380</v>
+      </c>
+      <c r="H15" s="6">
+        <v>41911</v>
+      </c>
+      <c r="I15" s="6">
+        <v>2752</v>
+      </c>
+      <c r="J15" s="6">
+        <v>1723</v>
+      </c>
+      <c r="K15" s="6">
+        <v>628</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0.99332534656854354</v>
+      </c>
       <c r="M15" s="10"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
+      <c r="N15" s="14">
+        <v>30798</v>
+      </c>
+      <c r="O15" s="14">
+        <v>468</v>
+      </c>
+      <c r="P15" s="14">
+        <v>14583</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>15447</v>
+      </c>
+      <c r="R15" s="14">
+        <v>838</v>
+      </c>
+      <c r="S15" s="14">
+        <v>413</v>
+      </c>
+      <c r="T15" s="14">
+        <v>197</v>
+      </c>
+      <c r="U15" s="14">
+        <v>62744</v>
+      </c>
       <c r="V15" s="10"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-      <c r="AA15" s="17"/>
+      <c r="W15" s="14">
+        <v>17776</v>
+      </c>
+      <c r="X15" s="14">
+        <v>7451</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>5540</v>
+      </c>
+      <c r="Z15" s="14">
+        <v>3448</v>
+      </c>
+      <c r="AA15" s="14">
+        <v>707</v>
+      </c>
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="9">

--- a/update.xlsx
+++ b/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dchholdingsltd-my.sharepoint.com/personal/kimtsang_dchauriga_com/Documents/Documents/AI Transportation KPI Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{C7812C41-A0D8-4678-A7FF-CC765441959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956D3AEE-A247-497E-86A9-6C88E7818173}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{C7812C41-A0D8-4678-A7FF-CC765441959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC511AC2-770C-4336-A162-8B09297CEC64}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
@@ -881,19 +881,23 @@
   <dimension ref="A1:AA23"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" customWidth="1"/>
-    <col min="13" max="13" width="1.77734375" style="12" customWidth="1"/>
-    <col min="14" max="14" width="17.21875" customWidth="1"/>
-    <col min="15" max="20" width="15.33203125" customWidth="1"/>
-    <col min="21" max="21" width="12.77734375" customWidth="1"/>
-    <col min="22" max="22" width="1.77734375" style="12" customWidth="1"/>
-    <col min="23" max="27" width="17.5546875" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.77734375" style="12" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" customWidth="1"/>
+    <col min="18" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="1.77734375" style="12" hidden="1" customWidth="1"/>
+    <col min="23" max="27" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="43.2">
@@ -1014,7 +1018,7 @@
       </c>
       <c r="M2" s="10"/>
       <c r="N2" s="14">
-        <v>21435</v>
+        <v>31965</v>
       </c>
       <c r="O2" s="14">
         <v>418</v>
@@ -1023,7 +1027,7 @@
         <v>15236</v>
       </c>
       <c r="Q2" s="14">
-        <v>8839</v>
+        <v>14761</v>
       </c>
       <c r="R2" s="14">
         <v>987</v>
@@ -1035,8 +1039,7 @@
         <v>221</v>
       </c>
       <c r="U2" s="14">
-        <f>SUM(N2:T2)</f>
-        <v>47511</v>
+        <v>63963</v>
       </c>
       <c r="V2" s="10"/>
       <c r="W2" s="14">
@@ -1094,7 +1097,7 @@
       </c>
       <c r="M3" s="10"/>
       <c r="N3" s="14">
-        <v>21070</v>
+        <v>31302</v>
       </c>
       <c r="O3" s="14">
         <v>388</v>
@@ -1103,7 +1106,7 @@
         <v>14785</v>
       </c>
       <c r="Q3" s="14">
-        <v>8582</v>
+        <v>14486</v>
       </c>
       <c r="R3" s="14">
         <v>984</v>
@@ -1115,8 +1118,7 @@
         <v>242</v>
       </c>
       <c r="U3" s="14">
-        <f t="shared" ref="U3:U14" si="0">SUM(N3:T3)</f>
-        <v>46456</v>
+        <v>62592</v>
       </c>
       <c r="V3" s="10"/>
       <c r="W3" s="14">
@@ -1174,7 +1176,7 @@
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="14">
-        <v>21223</v>
+        <v>31205</v>
       </c>
       <c r="O4" s="14">
         <v>433</v>
@@ -1183,7 +1185,7 @@
         <v>14829</v>
       </c>
       <c r="Q4" s="14">
-        <v>9020</v>
+        <v>16120</v>
       </c>
       <c r="R4" s="14">
         <v>906</v>
@@ -1195,8 +1197,7 @@
         <v>304</v>
       </c>
       <c r="U4" s="14">
-        <f t="shared" si="0"/>
-        <v>47086</v>
+        <v>64168</v>
       </c>
       <c r="V4" s="10"/>
       <c r="W4" s="14">
@@ -1254,7 +1255,7 @@
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="14">
-        <v>22139</v>
+        <v>31865</v>
       </c>
       <c r="O5" s="14">
         <v>462</v>
@@ -1263,7 +1264,7 @@
         <v>14906</v>
       </c>
       <c r="Q5" s="14">
-        <v>9120</v>
+        <v>15164</v>
       </c>
       <c r="R5" s="14">
         <v>1004</v>
@@ -1275,8 +1276,7 @@
         <v>271</v>
       </c>
       <c r="U5" s="14">
-        <f t="shared" si="0"/>
-        <v>48293</v>
+        <v>64063</v>
       </c>
       <c r="V5" s="10"/>
       <c r="W5" s="14">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="14">
-        <v>22216</v>
+        <v>30467</v>
       </c>
       <c r="O6" s="14">
         <v>412</v>
@@ -1343,7 +1343,7 @@
         <v>14526</v>
       </c>
       <c r="Q6" s="14">
-        <v>8541</v>
+        <v>14349</v>
       </c>
       <c r="R6" s="14">
         <v>920</v>
@@ -1355,8 +1355,7 @@
         <v>300</v>
       </c>
       <c r="U6" s="14">
-        <f t="shared" si="0"/>
-        <v>47359</v>
+        <v>61418</v>
       </c>
       <c r="V6" s="10"/>
       <c r="W6" s="14">
@@ -1414,7 +1413,7 @@
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="14">
-        <v>22127</v>
+        <v>32495</v>
       </c>
       <c r="O7" s="14">
         <v>449</v>
@@ -1423,7 +1422,7 @@
         <v>15626</v>
       </c>
       <c r="Q7" s="14">
-        <v>9278</v>
+        <v>16014</v>
       </c>
       <c r="R7" s="14">
         <v>968</v>
@@ -1435,8 +1434,7 @@
         <v>232</v>
       </c>
       <c r="U7" s="14">
-        <f t="shared" si="0"/>
-        <v>49097</v>
+        <v>66201</v>
       </c>
       <c r="V7" s="10"/>
       <c r="W7" s="14">
@@ -1494,7 +1492,6 @@
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="14">
-        <f>23707+9844</f>
         <v>33551</v>
       </c>
       <c r="O8" s="14">
@@ -1504,7 +1501,7 @@
         <v>15044</v>
       </c>
       <c r="Q8" s="14">
-        <v>9212</v>
+        <v>15135</v>
       </c>
       <c r="R8" s="14">
         <v>1087</v>
@@ -1516,8 +1513,7 @@
         <v>198</v>
       </c>
       <c r="U8" s="14">
-        <f t="shared" si="0"/>
-        <v>59960</v>
+        <v>65883</v>
       </c>
       <c r="V8" s="10"/>
       <c r="W8" s="14">
@@ -1575,7 +1571,6 @@
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="14">
-        <f>16936+7764</f>
         <v>24700</v>
       </c>
       <c r="O9" s="14">
@@ -1585,7 +1580,7 @@
         <v>13203</v>
       </c>
       <c r="Q9" s="14">
-        <v>7612</v>
+        <v>12793</v>
       </c>
       <c r="R9" s="14">
         <v>762</v>
@@ -1597,8 +1592,7 @@
         <v>218</v>
       </c>
       <c r="U9" s="14">
-        <f t="shared" si="0"/>
-        <v>47236</v>
+        <v>52417</v>
       </c>
       <c r="V9" s="10"/>
       <c r="W9" s="14">
@@ -1656,7 +1650,6 @@
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="14">
-        <f>21620+9596</f>
         <v>31216</v>
       </c>
       <c r="O10" s="14">
@@ -1666,7 +1659,7 @@
         <v>15525</v>
       </c>
       <c r="Q10" s="14">
-        <v>8866</v>
+        <v>16464</v>
       </c>
       <c r="R10" s="14">
         <v>952</v>
@@ -1678,8 +1671,7 @@
         <v>264</v>
       </c>
       <c r="U10" s="14">
-        <f t="shared" si="0"/>
-        <v>57704</v>
+        <v>65302</v>
       </c>
       <c r="V10" s="10"/>
       <c r="W10" s="14">
@@ -1737,7 +1729,6 @@
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="14">
-        <f>21187+8201</f>
         <v>29388</v>
       </c>
       <c r="O11" s="14">
@@ -1747,7 +1738,7 @@
         <v>14049</v>
       </c>
       <c r="Q11" s="14">
-        <v>8342</v>
+        <v>13832</v>
       </c>
       <c r="R11" s="14">
         <v>824</v>
@@ -1759,8 +1750,7 @@
         <v>264</v>
       </c>
       <c r="U11" s="14">
-        <f t="shared" si="0"/>
-        <v>53741</v>
+        <v>59231</v>
       </c>
       <c r="V11" s="10"/>
       <c r="W11" s="14">
@@ -1818,7 +1808,6 @@
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="14">
-        <f>20972+8220</f>
         <v>29192</v>
       </c>
       <c r="O12" s="14">
@@ -1828,7 +1817,7 @@
         <v>14296</v>
       </c>
       <c r="Q12" s="14">
-        <v>8077</v>
+        <v>14061</v>
       </c>
       <c r="R12" s="14">
         <v>837</v>
@@ -1840,8 +1829,7 @@
         <v>297</v>
       </c>
       <c r="U12" s="14">
-        <f t="shared" si="0"/>
-        <v>53663</v>
+        <v>59647</v>
       </c>
       <c r="V12" s="10"/>
       <c r="W12" s="14">
@@ -1899,7 +1887,6 @@
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="14">
-        <f>21874+9405</f>
         <v>31279</v>
       </c>
       <c r="O13" s="14">
@@ -1909,7 +1896,7 @@
         <v>14721</v>
       </c>
       <c r="Q13" s="14">
-        <v>9395</v>
+        <v>16540</v>
       </c>
       <c r="R13" s="14">
         <v>920</v>
@@ -1921,8 +1908,7 @@
         <v>204</v>
       </c>
       <c r="U13" s="14">
-        <f t="shared" si="0"/>
-        <v>57479</v>
+        <v>64624</v>
       </c>
       <c r="V13" s="10"/>
       <c r="W13" s="14">
@@ -2001,7 +1987,6 @@
         <v>237</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="0"/>
         <v>65761</v>
       </c>
       <c r="V14" s="10"/>
@@ -2229,7 +2214,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/update.xlsx
+++ b/update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dchholdingsltd-my.sharepoint.com/personal/kimtsang_dchauriga_com/Documents/Documents/AI Transportation KPI Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{C7812C41-A0D8-4678-A7FF-CC765441959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC511AC2-770C-4336-A162-8B09297CEC64}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{C7812C41-A0D8-4678-A7FF-CC765441959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6962947D-98F8-433D-8218-1A0AF4CF3DA7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2089,32 +2089,80 @@
       <c r="A16" s="9">
         <v>46266</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="7"/>
+      <c r="B16" s="6">
+        <v>10378</v>
+      </c>
+      <c r="C16" s="6">
+        <v>5.3</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="E16" s="6">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F16" s="6">
+        <v>55238</v>
+      </c>
+      <c r="G16" s="6">
+        <v>3699</v>
+      </c>
+      <c r="H16" s="6">
+        <v>53610</v>
+      </c>
+      <c r="I16" s="6">
+        <v>3100</v>
+      </c>
+      <c r="J16" s="6">
+        <v>1628</v>
+      </c>
+      <c r="K16" s="6">
+        <v>599</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0.99254758533899634</v>
+      </c>
       <c r="M16" s="10"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
+      <c r="N16" s="14">
+        <v>33875</v>
+      </c>
+      <c r="O16" s="14">
+        <v>526</v>
+      </c>
+      <c r="P16" s="14">
+        <v>14826</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>16806</v>
+      </c>
+      <c r="R16" s="14">
+        <v>873</v>
+      </c>
+      <c r="S16" s="14">
+        <v>436</v>
+      </c>
+      <c r="T16" s="14">
+        <v>249</v>
+      </c>
+      <c r="U16" s="14">
+        <v>67591</v>
+      </c>
       <c r="V16" s="10"/>
-      <c r="W16" s="17"/>
-      <c r="X16" s="17"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="17"/>
-      <c r="AA16" s="17"/>
+      <c r="W16" s="14">
+        <v>19254</v>
+      </c>
+      <c r="X16" s="14">
+        <v>7473</v>
+      </c>
+      <c r="Y16" s="14">
+        <v>5502</v>
+      </c>
+      <c r="Z16" s="14">
+        <v>4172</v>
+      </c>
+      <c r="AA16" s="14">
+        <v>712</v>
+      </c>
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="9">
